--- a/odk/source/crop_sown_registry_plan.xlsx
+++ b/odk/source/crop_sown_registry_plan.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -716,6 +716,11 @@
           <t>repeat_count</t>
         </is>
       </c>
+      <c r="O1" s="37" t="inlineStr">
+        <is>
+          <t>required_message</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="15" customFormat="1" customHeight="1" s="41">
       <c r="A2" s="41" t="inlineStr">
@@ -783,7 +788,7 @@
           <t>Farmer ID must be in format FR-1234567890.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="37" t="inlineStr">
         <is>
           <t>not(selected(${is_farmer_registered}, 'yes'))</t>
         </is>
@@ -878,6 +883,11 @@
       <c r="K6" s="46" t="n"/>
       <c r="L6" s="46" t="n"/>
       <c r="M6" s="46" t="n"/>
+      <c r="O6" s="37" t="inlineStr">
+        <is>
+          <t>Enter the Fayda ID (FAN).</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A7" s="46" t="inlineStr">
@@ -944,6 +954,11 @@
       <c r="K8" s="46" t="n"/>
       <c r="L8" s="46" t="n"/>
       <c r="M8" s="46" t="n"/>
+      <c r="O8" s="37" t="inlineStr">
+        <is>
+          <t>Select the production season.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="15" customFormat="1" customHeight="1" s="49">
       <c r="A9" s="50" t="inlineStr">
@@ -1140,10 +1155,14 @@
       </c>
       <c r="C15" s="46" t="inlineStr">
         <is>
-          <t>Geo Latitude</t>
-        </is>
-      </c>
-      <c r="D15" s="47" t="n"/>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="D15" s="47" t="inlineStr">
+        <is>
+          <t>In decimal degrees, for example 9.0301.</t>
+        </is>
+      </c>
       <c r="E15" s="46" t="n"/>
       <c r="F15" s="42" t="n"/>
       <c r="G15" s="44" t="n"/>
@@ -1167,10 +1186,14 @@
       </c>
       <c r="C16" s="46" t="inlineStr">
         <is>
-          <t>Geo Longitude</t>
-        </is>
-      </c>
-      <c r="D16" s="47" t="n"/>
+          <t>Longitude</t>
+        </is>
+      </c>
+      <c r="D16" s="47" t="inlineStr">
+        <is>
+          <t>In decimal degrees, for example 38.7469.</t>
+        </is>
+      </c>
       <c r="E16" s="46" t="n"/>
       <c r="F16" s="42" t="n"/>
       <c r="G16" s="44" t="n"/>
@@ -1287,6 +1310,11 @@
       <c r="L20" s="46" t="n"/>
       <c r="M20" s="46" t="n"/>
       <c r="N20" s="37" t="n"/>
+      <c r="O20" s="37" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A21" s="46" t="inlineStr">
@@ -1601,6 +1629,11 @@
         </is>
       </c>
       <c r="L30" s="46" t="n"/>
+      <c r="O30" s="37" t="inlineStr">
+        <is>
+          <t>Select the season.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A31" s="46" t="inlineStr">
@@ -1615,7 +1648,7 @@
       </c>
       <c r="C31" s="46" t="inlineStr">
         <is>
-          <t>Start GC</t>
+          <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D31" s="46" t="n"/>
@@ -1641,7 +1674,7 @@
       </c>
       <c r="C32" s="46" t="inlineStr">
         <is>
-          <t>End GC</t>
+          <t>End Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D32" s="46" t="n"/>
@@ -1827,7 +1860,7 @@
       </c>
       <c r="C38" s="46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crop </t>
+          <t>Crop</t>
         </is>
       </c>
       <c r="D38" s="46" t="n"/>
@@ -1849,6 +1882,11 @@
       <c r="L38" s="46" t="n"/>
       <c r="M38" s="42" t="n"/>
       <c r="N38" s="43" t="n"/>
+      <c r="O38" s="37" t="inlineStr">
+        <is>
+          <t>Select the crop.</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="15" customHeight="1" s="45">
       <c r="A39" s="60" t="inlineStr">
@@ -2029,7 +2067,7 @@
       </c>
       <c r="C45" s="46" t="inlineStr">
         <is>
-          <t>Planned Date (GC)</t>
+          <t>Planned Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D45" s="46" t="n"/>
@@ -2041,7 +2079,7 @@
       </c>
       <c r="G45" s="46" t="inlineStr">
         <is>
-          <t>Planned Date must be between Start GC and End GC.</t>
+          <t>Planned Date must be between Start Date and End Date.</t>
         </is>
       </c>
       <c r="H45" s="46" t="n"/>
@@ -2401,7 +2439,7 @@
       </c>
       <c r="C58" s="46" t="inlineStr">
         <is>
-          <t>Planned Labor</t>
+          <t>Planned Labour</t>
         </is>
       </c>
       <c r="D58" s="46" t="n"/>
@@ -2449,7 +2487,7 @@
       </c>
       <c r="C60" s="46" t="inlineStr">
         <is>
-          <t>Water Resource</t>
+          <t>Water Source</t>
         </is>
       </c>
       <c r="D60" s="46" t="n"/>
@@ -2469,6 +2507,11 @@
         </is>
       </c>
       <c r="L60" s="46" t="n"/>
+      <c r="O60" s="37" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A61" s="46" t="inlineStr">
@@ -2483,7 +2526,7 @@
       </c>
       <c r="C61" s="46" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Irrigation Method</t>
         </is>
       </c>
       <c r="D61" s="46" t="n"/>
@@ -2509,7 +2552,7 @@
       </c>
       <c r="C62" s="46" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Irrigation Frequency</t>
         </is>
       </c>
       <c r="D62" s="46" t="n"/>
@@ -2549,7 +2592,7 @@
       </c>
       <c r="C64" s="46" t="inlineStr">
         <is>
-          <t>DA Name</t>
+          <t>Development Agent Name</t>
         </is>
       </c>
       <c r="D64" s="46" t="n"/>
@@ -2561,7 +2604,7 @@
       </c>
       <c r="G64" s="42" t="inlineStr">
         <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H64" s="46" t="n"/>
@@ -2583,12 +2626,12 @@
       </c>
       <c r="C65" s="46" t="inlineStr">
         <is>
-          <t>DA Mobile Number</t>
+          <t>Development Agent Mobile Number</t>
         </is>
       </c>
       <c r="D65" s="42" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E65" s="46" t="n"/>
@@ -2599,7 +2642,7 @@
       </c>
       <c r="G65" s="42" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H65" s="42" t="n"/>
@@ -2633,7 +2676,7 @@
       </c>
       <c r="G66" s="42" t="inlineStr">
         <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H66" s="46" t="n"/>
@@ -2660,7 +2703,7 @@
       </c>
       <c r="D67" s="42" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E67" s="46" t="n"/>
@@ -2671,7 +2714,7 @@
       </c>
       <c r="G67" s="42" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H67" s="46" t="n"/>
@@ -2763,6 +2806,11 @@
       <c r="L70" s="46" t="n"/>
       <c r="M70" s="46" t="n"/>
       <c r="N70" s="37" t="n"/>
+      <c r="O70" s="37" t="inlineStr">
+        <is>
+          <t>Enter the Land ID.</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A71" s="46" t="inlineStr">
@@ -2777,7 +2825,7 @@
       </c>
       <c r="C71" s="61" t="inlineStr">
         <is>
-          <t>FPC Name</t>
+          <t>Farmer Production Cluster (FPC) Name</t>
         </is>
       </c>
       <c r="D71" s="46" t="n"/>
@@ -2831,6 +2879,11 @@
         </is>
       </c>
       <c r="L72" s="46" t="n"/>
+      <c r="O72" s="37" t="inlineStr">
+        <is>
+          <t>Select the season.</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A73" s="46" t="inlineStr">
@@ -2845,7 +2898,7 @@
       </c>
       <c r="C73" s="46" t="inlineStr">
         <is>
-          <t>Start GC</t>
+          <t>Start Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D73" s="46" t="n"/>
@@ -2871,7 +2924,7 @@
       </c>
       <c r="C74" s="46" t="inlineStr">
         <is>
-          <t>End GC</t>
+          <t>End Date (Gregorian calendar)</t>
         </is>
       </c>
       <c r="D74" s="46" t="n"/>
@@ -3256,7 +3309,11 @@
           <t>Total Cultivated Area (Timad)</t>
         </is>
       </c>
-      <c r="D86" s="50" t="n"/>
+      <c r="D86" s="50" t="inlineStr">
+        <is>
+          <t>One Timad is 0.25 hectare.</t>
+        </is>
+      </c>
       <c r="E86" s="50" t="n"/>
       <c r="F86" s="50" t="inlineStr">
         <is>
@@ -3343,7 +3400,7 @@
       </c>
       <c r="C89" s="46" t="inlineStr">
         <is>
-          <t>Plan (ha)</t>
+          <t>Planned Area (ha)</t>
         </is>
       </c>
       <c r="D89" s="50" t="n"/>
@@ -3355,7 +3412,7 @@
       </c>
       <c r="G89" s="42" t="inlineStr">
         <is>
-          <t>Plan (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
+          <t>Planned Area (ha) must be 0 or greater and cannot be greater than Total Cultivated Area (ha).</t>
         </is>
       </c>
       <c r="H89" s="50" t="n"/>
@@ -3377,7 +3434,7 @@
       </c>
       <c r="C90" s="46" t="inlineStr">
         <is>
-          <t>Collected Land (Quintal)</t>
+          <t>Collected Land (quintals)</t>
         </is>
       </c>
       <c r="D90" s="50" t="n"/>
@@ -3389,7 +3446,7 @@
       </c>
       <c r="G90" s="42" t="inlineStr">
         <is>
-          <t>Collected Land (Quintal) cannot be negative.</t>
+          <t>Collected Land (quintals) cannot be negative.</t>
         </is>
       </c>
       <c r="H90" s="50" t="n"/>
@@ -3411,7 +3468,7 @@
       </c>
       <c r="C91" s="46" t="inlineStr">
         <is>
-          <t>Collected Quintal</t>
+          <t>Quantity Collected (quintals)</t>
         </is>
       </c>
       <c r="D91" s="50" t="n"/>
@@ -3423,7 +3480,7 @@
       </c>
       <c r="G91" s="42" t="inlineStr">
         <is>
-          <t>Collected Quintal cannot be negative.</t>
+          <t>Quantity Collected cannot be negative.</t>
         </is>
       </c>
       <c r="H91" s="50" t="n"/>
@@ -3445,7 +3502,7 @@
       </c>
       <c r="C92" s="46" t="inlineStr">
         <is>
-          <t>Collected by Combiner (ha)</t>
+          <t>Area Collected by Combine Harvester (ha)</t>
         </is>
       </c>
       <c r="D92" s="50" t="n"/>
@@ -3457,7 +3514,7 @@
       </c>
       <c r="G92" s="42" t="inlineStr">
         <is>
-          <t>Collected by Combiner (ha) must be 0 or greater and cannot exceed Plan (ha).</t>
+          <t>Area Collected by Combine Harvester (ha) must be 0 or greater and cannot exceed Planned Area (ha).</t>
         </is>
       </c>
       <c r="H92" s="50" t="n"/>
@@ -3493,7 +3550,7 @@
       </c>
       <c r="C94" s="46" t="inlineStr">
         <is>
-          <t>Water Resource</t>
+          <t>Water Source</t>
         </is>
       </c>
       <c r="D94" s="46" t="n"/>
@@ -3513,6 +3570,11 @@
         </is>
       </c>
       <c r="L94" s="46" t="n"/>
+      <c r="O94" s="37" t="inlineStr">
+        <is>
+          <t>Select the water source.</t>
+        </is>
+      </c>
     </row>
     <row r="95" ht="15" customFormat="1" customHeight="1" s="37">
       <c r="A95" s="46" t="inlineStr">
@@ -3527,7 +3589,7 @@
       </c>
       <c r="C95" s="46" t="inlineStr">
         <is>
-          <t>Method</t>
+          <t>Irrigation Method</t>
         </is>
       </c>
       <c r="D95" s="46" t="n"/>
@@ -3553,7 +3615,7 @@
       </c>
       <c r="C96" s="46" t="inlineStr">
         <is>
-          <t>Frequency</t>
+          <t>Irrigation Frequency</t>
         </is>
       </c>
       <c r="D96" s="46" t="n"/>
@@ -3645,7 +3707,7 @@
       </c>
       <c r="C100" s="46" t="inlineStr">
         <is>
-          <t>DA Name</t>
+          <t>Development Agent Name</t>
         </is>
       </c>
       <c r="D100" s="46" t="n"/>
@@ -3657,7 +3719,7 @@
       </c>
       <c r="G100" s="42" t="inlineStr">
         <is>
-          <t>DA Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the Development Agent's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H100" s="46" t="n"/>
@@ -3679,12 +3741,12 @@
       </c>
       <c r="C101" s="46" t="inlineStr">
         <is>
-          <t>DA Mobile Number</t>
+          <t>Development Agent Mobile Number</t>
         </is>
       </c>
       <c r="D101" s="42" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E101" s="46" t="n"/>
@@ -3695,7 +3757,7 @@
       </c>
       <c r="G101" s="42" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H101" s="42" t="n"/>
@@ -3729,7 +3791,7 @@
       </c>
       <c r="G102" s="42" t="inlineStr">
         <is>
-          <t>Supervisor Name may contain only letters (English or Amharic), spaces, dots and hyphens</t>
+          <t>Enter the supervisor's name using letters (English or Amharic), spaces, dots and hyphens only.</t>
         </is>
       </c>
       <c r="H102" s="46" t="n"/>
@@ -3756,7 +3818,7 @@
       </c>
       <c r="D103" s="42" t="inlineStr">
         <is>
-          <t>Format: 0911223344 or +251911223344</t>
+          <t>For example 0911223344 or +251911223344</t>
         </is>
       </c>
       <c r="E103" s="46" t="n"/>
@@ -3767,7 +3829,7 @@
       </c>
       <c r="G103" s="42" t="inlineStr">
         <is>
-          <t>Enter valid Ethiopian number: 0911223344 or +251911223344</t>
+          <t>Enter a valid Ethiopian mobile number, for example 0911223344 or +251911223344.</t>
         </is>
       </c>
       <c r="H103" s="46" t="n"/>
@@ -4768,7 +4830,7 @@
       </c>
       <c r="C23" s="42" t="inlineStr">
         <is>
-          <t>Farmer-to-Farmer Exchange /Saved Seed</t>
+          <t>Farmer-to-Farmer Exchange / Saved Seed</t>
         </is>
       </c>
       <c r="D23" s="42" t="n"/>
@@ -5365,7 +5427,7 @@
       </c>
       <c r="C57" s="47" t="inlineStr">
         <is>
-          <t>Bi-weekly</t>
+          <t>Every two weeks</t>
         </is>
       </c>
       <c r="D57" s="43" t="n"/>
@@ -5551,7 +5613,7 @@
       </c>
       <c r="C67" s="72" t="inlineStr">
         <is>
-          <t>Nps</t>
+          <t>NPS</t>
         </is>
       </c>
       <c r="D67" s="43" t="n"/>
@@ -5572,7 +5634,7 @@
       </c>
       <c r="C68" s="72" t="inlineStr">
         <is>
-          <t>Npsb</t>
+          <t>NPSB</t>
         </is>
       </c>
       <c r="D68" s="43" t="n"/>
@@ -5593,7 +5655,7 @@
       </c>
       <c r="C69" s="72" t="inlineStr">
         <is>
-          <t>Dap</t>
+          <t>DAP</t>
         </is>
       </c>
       <c r="D69" s="43" t="n"/>
@@ -11845,7 +11907,7 @@
     <row r="2" ht="15" customHeight="1" s="45">
       <c r="A2" s="37" t="inlineStr">
         <is>
-          <t>CSR – 1. Planning</t>
+          <t>Crop Sown Registry - 1. Planning</t>
         </is>
       </c>
       <c r="B2" s="37" t="inlineStr">
